--- a/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_65064_completo.xlsx
+++ b/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_65064_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R037ffc5d0cf5480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R44f2aae01cab4949"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,351 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.7619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.0658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.5217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.9776</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.2815</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.7374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.1933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.1933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.3943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.3943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.6982</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_65064_completo.xlsx
+++ b/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_65064_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R44f2aae01cab4949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3c543b07ea324165"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2361 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.9212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.8506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.4938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.1369</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.7840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.4977</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0266</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.0021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.6737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.1296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.7374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.3486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.9212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.4232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.8546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    148.5056</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    171.5096</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    192.8704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    196.1567</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    206.0155</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    227.3764</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    132.0742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3566</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     71.2781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.0413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.1933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.4972</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.3486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.9212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.0663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.9957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.8546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.9997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.7840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.6389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.1409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.8506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.2423</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.8502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.7374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.3452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.7761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.0624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.3486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.6349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.5643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.8506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.4232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.3526</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.9957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.5683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.1409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.1409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.7840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.7840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.9997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     95.9252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.9139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.0658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.3698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.9776</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.4335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.7374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.0413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.4972</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.8506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.8506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.0663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.7095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.3526</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.6389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.5683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.2114</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.4977</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.8585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.6389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.3060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.2423</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.6982</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.8502</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.0021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.0021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.3060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.3060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.9139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.0658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.2178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.2178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.5217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.8256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.2815</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.4972</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.7761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.6389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2154</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     71.2781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.6982</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.6982</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.0021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
